--- a/corpus/xlsx/level-011/template.xlsx
+++ b/corpus/xlsx/level-011/template.xlsx
@@ -30,57 +30,57 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{{title}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{customer}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{count}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{spaced}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{enabled}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{literal}}</t>
+      <t xml:space="preserve">{d.title}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.customer}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.count}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.spaced}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.enabled}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.literal}</t>
     </r>
   </si>
 </sst>
